--- a/5/search/FY4_Missile1_results/best_solution.xlsx
+++ b/5/search/FY4_Missile1_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>315</v>
+        <v>265.5</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>122</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
       <c r="E2" t="n">
-        <v>12092.90424100193</v>
+        <v>10961.71196128481</v>
       </c>
       <c r="F2" t="n">
-        <v>907.0957589980717</v>
+        <v>1513.504341138233</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>13003.6577751702</v>
+        <v>10846.84784513925</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.65777517020183</v>
+        <v>54.01736455293417</v>
       </c>
       <c r="J2" t="n">
-        <v>1310</v>
+        <v>1094.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
